--- a/etf_holdings/2026-08-24_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-24_active_etf_full_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:40</t>
+          <t>2026-08-24 16:23:48</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:41</t>
+          <t>2026-08-24 16:23:50</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:42</t>
+          <t>2026-08-24 16:23:51</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:44</t>
+          <t>2026-08-24 16:23:52</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:44</t>
+          <t>2026-08-24 16:23:52</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:44</t>
+          <t>2026-08-24 16:23:52</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:44</t>
+          <t>2026-08-24 16:23:52</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:44</t>
+          <t>2026-08-24 16:23:52</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:49</t>
+          <t>2026-08-24 16:23:58</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:50</t>
+          <t>2026-08-24 16:23:59</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:51</t>
+          <t>2026-08-24 16:24:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:52</t>
+          <t>2026-08-24 16:24:01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:52</t>
+          <t>2026-08-24 16:24:01</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:52</t>
+          <t>2026-08-24 16:24:01</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:52</t>
+          <t>2026-08-24 16:24:01</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:52</t>
+          <t>2026-08-24 16:24:01</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13263,17 +13263,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>2330台灣積體電路製造</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -13299,20 +13299,20 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>17.12%12,000,000</t>
+          <t>13.98%588,000</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>17.12%</t>
+          <t>13.98%</t>
         </is>
       </c>
       <c r="K211" t="n">
-        <v>12000000</v>
+        <v>588000</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -13324,17 +13324,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -13342,38 +13342,38 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+0.44%341</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>5430</v>
+        <v>341</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>5.68%1,690,000</t>
+          <t>4.85%1,448,000</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="K212" t="n">
-        <v>1690000</v>
+        <v>1448000</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -13385,17 +13385,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -13403,38 +13403,38 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>-0.4%250.5</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1075</v>
+        <v>250.5</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>5.43%8,460,000</t>
+          <t>4.31%1,737,000</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="K213" t="n">
-        <v>8460000</v>
+        <v>1737000</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -13446,17 +13446,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -13464,38 +13464,38 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>4904遠傳電信</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>-0.98%101.5</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>2855</v>
+        <v>101.5</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>5.09%3,000,000</t>
+          <t>3.88%3,832,000</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K214" t="n">
-        <v>3000000</v>
+        <v>3832000</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -13507,17 +13507,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -13525,38 +13525,38 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H215" t="n">
-        <v>3765</v>
+        <v>136.5</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>4.73%2,110,000</t>
+          <t>3.81%2,828,000</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>3.81%</t>
         </is>
       </c>
       <c r="K215" t="n">
-        <v>2110000</v>
+        <v>2828000</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -13568,17 +13568,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -13586,38 +13586,38 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>+0.72%6300</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H216" t="n">
-        <v>123.5</v>
+        <v>6300</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>4.14%60,000,000</t>
+          <t>3.27%53,000</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K216" t="n">
-        <v>60000000</v>
+        <v>53000</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -13629,17 +13629,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -13647,38 +13647,38 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>-4.45%5155</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>-4.45%</t>
         </is>
       </c>
       <c r="H217" t="n">
-        <v>5565</v>
+        <v>5155</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>3.56%1,100,000</t>
+          <t>2.61%49,000</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K217" t="n">
-        <v>1100000</v>
+        <v>49000</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -13690,17 +13690,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -13708,38 +13708,38 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>+1.72%2070</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H218" t="n">
-        <v>5155</v>
+        <v>2070</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>3.45%1,080,000</t>
+          <t>2.49%124,000</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K218" t="n">
-        <v>1080000</v>
+        <v>124000</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -13751,17 +13751,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -13769,34 +13769,34 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>1504東元電機</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>-0.83%71.5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H219" t="n">
-        <v>551</v>
+        <v>71.5</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>3.21%9,785,000</t>
+          <t>2.47%3,473,000</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K219" t="n">
-        <v>9785000</v>
+        <v>3473000</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -13812,17 +13812,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -13830,38 +13830,38 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>-4.83%355</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1735</v>
+        <v>355</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>3.15%3,040,000</t>
+          <t>2.41%656,000</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K220" t="n">
-        <v>3040000</v>
+        <v>656000</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -13873,17 +13873,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -13891,38 +13891,38 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-5.31%2765</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H221" t="n">
-        <v>2070</v>
+        <v>2765</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2.78%2,307,000</t>
+          <t>2.39%83,000</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K221" t="n">
-        <v>2307000</v>
+        <v>83000</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -13934,17 +13934,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -13952,38 +13952,38 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-3.39%2140</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="H222" t="n">
-        <v>592</v>
+        <v>2140</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2.78%8,000,000</t>
+          <t>2.36%108,000</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K222" t="n">
-        <v>8000000</v>
+        <v>108000</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -13995,17 +13995,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -14013,38 +14013,38 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>-4.26%1460</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="H223" t="n">
-        <v>6300</v>
+        <v>1460</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2.26%610,000</t>
+          <t>2.23%148,000</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K223" t="n">
-        <v>610000</v>
+        <v>148000</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -14056,17 +14056,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -14074,25 +14074,25 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+1.39%51</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="H224" t="n">
-        <v>5385</v>
+        <v>51</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2.08%626,000</t>
+          <t>2.08%4,181,000</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14101,11 +14101,11 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>626000</v>
+        <v>4181000</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -14117,17 +14117,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:25:17</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -14135,38 +14135,38 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>-2.34%6255</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H225" t="n">
-        <v>794</v>
+        <v>6255</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2.04%4,250,000</t>
+          <t>1.96%31,000</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K225" t="n">
-        <v>4250000</v>
+        <v>31000</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -14178,17 +14178,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -14196,38 +14196,38 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-4.2%5365</t>
+          <t>+0.85%592</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H226" t="n">
-        <v>5365</v>
+        <v>592</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2.02%610,000</t>
+          <t>1.94%335,000</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K226" t="n">
-        <v>610000</v>
+        <v>335000</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -14239,17 +14239,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -14257,38 +14257,38 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-0.35%2855</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>1135</v>
+        <v>2855</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1.77%2,640,000</t>
+          <t>1.92%68,000</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="K227" t="n">
-        <v>2640000</v>
+        <v>68000</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -14300,17 +14300,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -14318,38 +14318,38 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>-0.66%3765</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>15115</v>
+        <v>3765</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1.63%179,500</t>
+          <t>1.87%50,000</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K228" t="n">
-        <v>179500</v>
+        <v>50000</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -14361,17 +14361,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -14379,38 +14379,38 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>+0.49%20.5</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>2050</v>
+        <v>20.5</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1.62%1,200,000</t>
+          <t>1.77%8,783,000</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K229" t="n">
-        <v>1200000</v>
+        <v>8783000</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -14422,17 +14422,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -14440,38 +14440,38 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-2.21%177</t>
+          <t>-0.92%1075</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>177</v>
+        <v>1075</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1.61%15,000,000</t>
+          <t>1.71%160,000</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K230" t="n">
-        <v>15000000</v>
+        <v>160000</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -14483,17 +14483,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -14501,34 +14501,34 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>-2.67%200.5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H231" t="n">
-        <v>1455</v>
+        <v>200.5</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1.59%1,800,000</t>
+          <t>1.60%788,000</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K231" t="n">
-        <v>1800000</v>
+        <v>788000</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -14544,17 +14544,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -14562,38 +14562,38 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>+0.32%157</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="H232" t="n">
-        <v>1010</v>
+        <v>157</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>1.56%2,800,000</t>
+          <t>1.57%1,019,000</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K232" t="n">
-        <v>2800000</v>
+        <v>1019000</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -14605,17 +14605,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -14623,38 +14623,38 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>+5.36%1475</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+5.36%</t>
         </is>
       </c>
       <c r="H233" t="n">
-        <v>2070</v>
+        <v>1475</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>1.24%1,000,000</t>
+          <t>1.49%108,000</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K233" t="n">
-        <v>1000000</v>
+        <v>108000</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -14666,17 +14666,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -14684,38 +14684,38 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+7.66%14410</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>1145</v>
+        <v>14410</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1.03%1,600,000</t>
+          <t>1.45%11,000</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K234" t="n">
-        <v>1600000</v>
+        <v>11000</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -14727,17 +14727,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -14745,38 +14745,38 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-6.25%180</t>
+          <t>-0.86%1735</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>180</v>
+        <v>1735</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1.02%9,000,000</t>
+          <t>1.42%82,000</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K235" t="n">
-        <v>9000000</v>
+        <v>82000</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -14788,17 +14788,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -14806,38 +14806,38 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>+0.75%269.5</t>
+          <t>-4.4%5430</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>269.5</v>
+        <v>5430</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>0.85%5,360,000</t>
+          <t>1.29%23,000</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K236" t="n">
-        <v>5360000</v>
+        <v>23000</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -14849,17 +14849,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -14867,38 +14867,38 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-3.12%1710</t>
+          <t>-0.13%77.4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H237" t="n">
-        <v>1710</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>0.73%700,000</t>
+          <t>1.27%1,657,000</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K237" t="n">
-        <v>700000</v>
+        <v>1657000</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -14910,17 +14910,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -14928,38 +14928,38 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-7.99%507</t>
+          <t>+5.05%1145</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>-7.99%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H238" t="n">
-        <v>507</v>
+        <v>1145</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>0.59%1,800,000</t>
+          <t>1.22%113,000</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K238" t="n">
-        <v>1800000</v>
+        <v>113000</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -14971,17 +14971,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -14989,38 +14989,38 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>+0.94%1610</t>
+          <t>-5.11%501</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-5.11%</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>1610</v>
+        <v>501</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>0.50%525,000</t>
+          <t>1.01%193,000</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K239" t="n">
-        <v>525000</v>
+        <v>193000</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -15032,17 +15032,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:25:18</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -15050,38 +15050,38 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-2.34%6255</t>
+          <t>+1.39%658</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="H240" t="n">
-        <v>6255</v>
+        <v>658</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>0.49%130,000</t>
+          <t>0.94%146,000</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K240" t="n">
-        <v>130000</v>
+        <v>146000</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -15093,17 +15093,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -15111,38 +15111,38 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-0.81%243.5</t>
+          <t>-1.76%948</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="H241" t="n">
-        <v>243.5</v>
+        <v>948</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>0.46%3,200,000</t>
+          <t>0.93%98,000</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K241" t="n">
-        <v>3200000</v>
+        <v>98000</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -15154,17 +15154,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -15172,34 +15172,34 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-6.99%326</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>-6.99%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>326</v>
+        <v>5385</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>0.41%2,000,000</t>
+          <t>0.66%12,000</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K242" t="n">
-        <v>2000000</v>
+        <v>12000</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -15215,17 +15215,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -15233,38 +15233,38 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>+1.22%124</t>
+          <t>+0.84%1205</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H243" t="n">
-        <v>124</v>
+        <v>1205</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>0.33%4,500,000</t>
+          <t>0.66%56,000</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K243" t="n">
-        <v>4500000</v>
+        <v>56000</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -15276,17 +15276,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -15294,38 +15294,38 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-2.27%688</t>
+          <t>0%1135</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H244" t="n">
-        <v>688</v>
+        <v>1135</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>0.33%800,000</t>
+          <t>0.54%48,000</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K244" t="n">
-        <v>800000</v>
+        <v>48000</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -15337,17 +15337,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -15355,38 +15355,38 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-4.36%417</t>
+          <t>-0.54%551</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H245" t="n">
-        <v>417</v>
+        <v>551</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>0.21%800,000</t>
+          <t>0.49%89,000</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K245" t="n">
-        <v>800000</v>
+        <v>89000</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -15398,17 +15398,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -15416,34 +15416,34 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>-4.26%1460</t>
+          <t>-1.25%435.5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>-4.26%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H246" t="n">
-        <v>1460</v>
+        <v>435.5</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>0.20%225,000</t>
+          <t>0.48%110,000</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K246" t="n">
-        <v>225000</v>
+        <v>110000</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -15459,17 +15459,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -15477,38 +15477,38 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-1.59%557</t>
+          <t>-2.21%177</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>557</v>
+        <v>177</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>0.17%500,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K247" t="n">
-        <v>500000</v>
+        <v>243000</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -15520,17 +15520,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -15538,38 +15538,38 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>+0.15%680</t>
+          <t>+2.89%2135</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H248" t="n">
-        <v>680</v>
+        <v>2135</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>0.16%393,000</t>
+          <t>0.41%20,000</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K248" t="n">
-        <v>393000</v>
+        <v>20000</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -15581,17 +15581,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -15599,38 +15599,38 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3131弘塑科技</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>+1.08%2335</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>14410</v>
+        <v>2335</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>0.16%20,000</t>
+          <t>0.27%12,000</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K249" t="n">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -15642,17 +15642,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -15660,38 +15660,38 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>+0.47%1065</t>
+          <t>-1.49%132</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H250" t="n">
-        <v>1065</v>
+        <v>132</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>0.16%250,000</t>
+          <t>0.20%154,000</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K250" t="n">
-        <v>250000</v>
+        <v>154000</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -15703,17 +15703,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -15721,34 +15721,34 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>-2.15%63.6</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>435.5</v>
+        <v>63.6</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>0.13%500,000</t>
+          <t>0.20%306,000</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K251" t="n">
-        <v>500000</v>
+        <v>306000</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -15764,17 +15764,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -15782,38 +15782,38 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-0.42%71.3</t>
+          <t>+6.01%123.5</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>+6.01%</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>71.3</v>
+        <v>123.5</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>0.11%2,500,000</t>
+          <t>0.20%171,000</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K252" t="n">
-        <v>2500000</v>
+        <v>171000</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -15825,17 +15825,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -15843,38 +15843,38 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>1802台灣玻璃工業</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>+1.23%205.5</t>
+          <t>-1.22%56.9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>205.5</v>
+        <v>56.9</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>0.08%700,000</t>
+          <t>0.20%357,000</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K253" t="n">
-        <v>700000</v>
+        <v>357000</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -15886,17 +15886,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -15904,38 +15904,38 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>-2.12%230.5</t>
+          <t>-9.89%2050</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>230.5</v>
+        <v>2050</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.20%9,000</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K254" t="n">
-        <v>350000</v>
+        <v>9000</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -15947,17 +15947,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:25:19</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -15965,34 +15965,34 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>-6.03%381.5</t>
+          <t>-1.58%343.5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>381.5</v>
+        <v>343.5</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>0.05%200,000</t>
+          <t>0.19%55,000</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K255" t="n">
-        <v>200000</v>
+        <v>55000</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -16008,17 +16008,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:25:20</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -16026,34 +16026,34 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>+2.89%2135</t>
+          <t>+2.09%2200</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>2135</v>
+        <v>2200</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.17%8,000</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K256" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -16069,17 +16069,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:25:20</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -16087,38 +16087,38 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>2317鴻海精密工業</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>+0.51%493</t>
+          <t>-0.81%243.5</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>493</v>
+        <v>243.5</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.16%64,000</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K257" t="n">
-        <v>1000</v>
+        <v>64000</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -16130,17 +16130,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:25:20</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -16148,38 +16148,38 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>-1.58%343.5</t>
+          <t>-1.43%2070</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>343.5</v>
+        <v>2070</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.10%5,000</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K258" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -16191,17 +16191,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:25:20</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -16209,38 +16209,38 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>6488環球晶圓</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>-0.33%151</t>
+          <t>+7.33%1010</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+7.33%</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>151</v>
+        <v>1010</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.09%10,000</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K259" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -16252,17 +16252,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:25:20</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -16270,38 +16270,38 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>+0.75%134</t>
+          <t>-2.1%794</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>134</v>
+        <v>794</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.02%2,000</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K260" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -16313,17 +16313,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -16331,38 +16331,38 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2330台灣積體電路製造</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+7.66%14410</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>2375</v>
+        <v>14410</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>13.98%588,000</t>
+          <t>8.30%260,000</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>13.98%</t>
+          <t>8.30%</t>
         </is>
       </c>
       <c r="K261" t="n">
-        <v>588000</v>
+        <v>260000</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -16374,17 +16374,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -16392,38 +16392,38 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2376技嘉科技</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>+0.44%341</t>
+          <t>-1.45%2375</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>341</v>
+        <v>2375</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>4.85%1,448,000</t>
+          <t>7.51%1,306,000</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>7.51%</t>
         </is>
       </c>
       <c r="K262" t="n">
-        <v>1448000</v>
+        <v>1306000</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -16435,17 +16435,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -16453,34 +16453,34 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>-0.4%250.5</t>
+          <t>-0.35%2855</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>250.5</v>
+        <v>2855</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>4.31%1,737,000</t>
+          <t>6.84%1,001,000</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="K263" t="n">
-        <v>1737000</v>
+        <v>1001000</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -16496,17 +16496,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -16514,38 +16514,38 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>4904遠傳電信</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>-0.98%101.5</t>
+          <t>-0.92%1075</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>101.5</v>
+        <v>1075</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>3.88%3,832,000</t>
+          <t>6.42%2,482,000</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="K264" t="n">
-        <v>3832000</v>
+        <v>2482000</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -16557,17 +16557,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -16575,38 +16575,38 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>0%136.5</t>
+          <t>-9.89%2050</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>136.5</v>
+        <v>2050</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>3.81%2,828,000</t>
+          <t>6.30%1,161,000</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>6.30%</t>
         </is>
       </c>
       <c r="K265" t="n">
-        <v>2828000</v>
+        <v>1161000</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -16618,17 +16618,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -16636,38 +16636,38 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>-4.4%5430</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>6300</v>
+        <v>5430</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>3.27%53,000</t>
+          <t>6.30%465,000</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>6.30%</t>
         </is>
       </c>
       <c r="K266" t="n">
-        <v>53000</v>
+        <v>465000</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -16679,17 +16679,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -16697,38 +16697,38 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>+1.72%2070</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H267" t="n">
-        <v>5155</v>
+        <v>2070</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2.61%49,000</t>
+          <t>5.21%1,074,000</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K267" t="n">
-        <v>49000</v>
+        <v>1074000</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -16740,17 +16740,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -16758,38 +16758,38 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>2070</v>
+        <v>5385</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2.49%124,000</t>
+          <t>4.59%343,000</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="K268" t="n">
-        <v>124000</v>
+        <v>343000</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -16801,17 +16801,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -16819,38 +16819,38 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1504東元電機</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>-0.83%71.5</t>
+          <t>+5.05%1145</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>71.5</v>
+        <v>1145</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2.47%3,473,000</t>
+          <t>4.24%1,630,000</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>4.24%</t>
         </is>
       </c>
       <c r="K269" t="n">
-        <v>3473000</v>
+        <v>1630000</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -16862,17 +16862,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -16880,38 +16880,38 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>3105穩懋半導體</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>-4.83%355</t>
+          <t>+1.83%5565</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>355</v>
+        <v>5565</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2.41%656,000</t>
+          <t>3.49%268,000</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K270" t="n">
-        <v>656000</v>
+        <v>268000</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -16923,17 +16923,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -16941,38 +16941,38 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>3081聯亞光電工業</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>-5.31%2765</t>
+          <t>-0.34%586</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>2765</v>
+        <v>586</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2.39%83,000</t>
+          <t>3.13%2,231,000</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K271" t="n">
-        <v>83000</v>
+        <v>2231000</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -16984,17 +16984,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -17002,38 +17002,38 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>7750新代科技</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>-3.39%2140</t>
+          <t>0%175.5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>2140</v>
+        <v>175.5</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2.36%108,000</t>
+          <t>3.03%7,245,000</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K272" t="n">
-        <v>108000</v>
+        <v>7245000</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -17045,17 +17045,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -17063,38 +17063,38 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>-4.26%1460</t>
+          <t>-4.02%107.5</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>-4.26%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>1460</v>
+        <v>107.5</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2.23%148,000</t>
+          <t>2.90%10,877,000</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K273" t="n">
-        <v>148000</v>
+        <v>10877000</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -17106,17 +17106,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -17124,38 +17124,38 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>+1.39%51</t>
+          <t>-6.03%381.5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>51</v>
+        <v>381.5</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2.08%4,181,000</t>
+          <t>2.67%2,753,000</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="K274" t="n">
-        <v>4181000</v>
+        <v>2753000</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -17167,17 +17167,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:15</t>
+          <t>2026-08-24 16:25:27</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -17185,38 +17185,38 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-2.34%6255</t>
+          <t>-0.86%1735</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>6255</v>
+        <v>1735</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>1.96%31,000</t>
+          <t>2.64%632,000</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K275" t="n">
-        <v>31000</v>
+        <v>632000</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -17228,17 +17228,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -17246,38 +17246,38 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-2.14%388.5</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>592</v>
+        <v>388.5</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>1.94%335,000</t>
+          <t>2.54%2,682,000</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K276" t="n">
-        <v>335000</v>
+        <v>2682000</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -17289,17 +17289,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -17307,38 +17307,38 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>-6.25%180</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-6.25%</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>2855</v>
+        <v>180</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>1.92%68,000</t>
+          <t>2.49%5,445,000</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K277" t="n">
-        <v>68000</v>
+        <v>5445000</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -17350,17 +17350,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17386,20 +17386,20 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>1.87%50,000</t>
+          <t>2.40%266,000</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K278" t="n">
-        <v>50000</v>
+        <v>266000</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -17411,17 +17411,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -17429,38 +17429,38 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>+0.49%20.5</t>
+          <t>-4.2%5365</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>20.5</v>
+        <v>5365</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>1.77%8,783,000</t>
+          <t>2.19%164,000</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K279" t="n">
-        <v>8783000</v>
+        <v>164000</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -17472,17 +17472,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -17490,38 +17490,38 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+0.95%3735</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>1075</v>
+        <v>3735</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>1.71%160,000</t>
+          <t>1.90%215,000</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K280" t="n">
-        <v>160000</v>
+        <v>215000</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -17533,17 +17533,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -17551,38 +17551,38 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-2.67%200.5</t>
+          <t>-2.1%794</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>200.5</v>
+        <v>794</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>1.60%788,000</t>
+          <t>1.63%844,013</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K281" t="n">
-        <v>788000</v>
+        <v>844013</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -17594,17 +17594,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -17612,38 +17612,38 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>+0.32%157</t>
+          <t>+0.72%6300</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>157</v>
+        <v>6300</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>1.57%1,019,000</t>
+          <t>1.15%77,000</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K282" t="n">
-        <v>1019000</v>
+        <v>77000</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -17655,17 +17655,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -17673,38 +17673,38 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>+5.36%1475</t>
+          <t>-1.25%435.5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>+5.36%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>1475</v>
+        <v>435.5</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>1.49%108,000</t>
+          <t>1.05%1,000,000</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K283" t="n">
-        <v>108000</v>
+        <v>1000000</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -17716,17 +17716,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -17734,38 +17734,38 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>+0.85%592</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>14410</v>
+        <v>592</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>1.45%11,000</t>
+          <t>1.00%716,000</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K284" t="n">
-        <v>11000</v>
+        <v>716000</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -17777,17 +17777,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -17795,38 +17795,38 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>0%1135</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>1735</v>
+        <v>1135</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>1.42%82,000</t>
+          <t>0.81%300,000</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K285" t="n">
-        <v>82000</v>
+        <v>300000</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -17838,17 +17838,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -17856,38 +17856,38 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>-5.95%482.5</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>5430</v>
+        <v>482.5</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>1.29%23,000</t>
+          <t>0.46%373,000</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K286" t="n">
-        <v>23000</v>
+        <v>373000</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -17899,17 +17899,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -17917,34 +17917,34 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>-0.13%77.4</t>
+          <t>-0.52%758</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>77.40000000000001</v>
+        <v>758</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>1.27%1,657,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K287" t="n">
-        <v>1657000</v>
+        <v>250000</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -17960,17 +17960,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -17978,38 +17978,38 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>-5.31%2765</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>1145</v>
+        <v>2765</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>1.22%113,000</t>
+          <t>0.44%63,000</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K288" t="n">
-        <v>113000</v>
+        <v>63000</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -18021,17 +18021,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -18039,38 +18039,38 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>-5.11%501</t>
+          <t>+0.22%923</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>501</v>
+        <v>923</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>1.01%193,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K289" t="n">
-        <v>193000</v>
+        <v>196000</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -18082,17 +18082,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:17</t>
+          <t>2026-08-24 16:25:29</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -18100,38 +18100,38 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>+1.39%658</t>
+          <t>-4.45%5155</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-4.45%</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>658</v>
+        <v>5155</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>0.94%146,000</t>
+          <t>0.42%33,000</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K290" t="n">
-        <v>146000</v>
+        <v>33000</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -18143,17 +18143,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -18161,38 +18161,38 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>-1.76%948</t>
+          <t>+0.44%341</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>948</v>
+        <v>341</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>0.93%98,000</t>
+          <t>0.41%508,000</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K291" t="n">
-        <v>98000</v>
+        <v>508000</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -18204,17 +18204,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -18222,38 +18222,38 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+9.96%287</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>5385</v>
+        <v>287</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>0.66%12,000</t>
+          <t>0.41%659,000</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K292" t="n">
-        <v>12000</v>
+        <v>659000</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -18265,17 +18265,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -18283,38 +18283,38 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>+0.84%1205</t>
+          <t>+1.15%87.7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>1205</v>
+        <v>87.7</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>0.66%56,000</t>
+          <t>0.40%1,957,000</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K293" t="n">
-        <v>56000</v>
+        <v>1957000</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -18326,17 +18326,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -18344,38 +18344,38 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>1135</v>
+        <v>1455</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>0.54%48,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K294" t="n">
-        <v>48000</v>
+        <v>113000</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -18387,17 +18387,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -18405,38 +18405,38 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>-1.53%15115</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>551</v>
+        <v>15115</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>0.49%89,000</t>
+          <t>0.40%11,000</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K295" t="n">
-        <v>89000</v>
+        <v>11000</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -18448,17 +18448,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -18466,38 +18466,38 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>+0.63%643</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>435.5</v>
+        <v>643</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>0.48%110,000</t>
+          <t>0.40%261,000</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>110000</v>
+        <v>261000</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -18509,17 +18509,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -18527,38 +18527,38 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>-2.21%177</t>
+          <t>+0.47%1065</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>177</v>
+        <v>1065</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>0.43%243,000</t>
+          <t>0.39%155,000</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>243000</v>
+        <v>155000</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -18570,17 +18570,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -18588,38 +18588,38 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>+2.89%2135</t>
+          <t>+0.84%1205</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>2135</v>
+        <v>1205</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>0.41%20,000</t>
+          <t>0.38%134,000</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K298" t="n">
-        <v>20000</v>
+        <v>134000</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -18631,17 +18631,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -18649,38 +18649,38 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>3131弘塑科技</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>+1.08%2335</t>
+          <t>-1.43%2070</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>2335</v>
+        <v>2070</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>0.27%12,000</t>
+          <t>0.38%76,000</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K299" t="n">
-        <v>12000</v>
+        <v>76000</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -18692,17 +18692,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -18710,38 +18710,38 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-1.49%132</t>
+          <t>+0.64%1570</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>132</v>
+        <v>1570</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>0.20%154,000</t>
+          <t>0.36%98,000</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K300" t="n">
-        <v>154000</v>
+        <v>98000</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -18753,17 +18753,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -18771,34 +18771,34 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-2.15%63.6</t>
+          <t>-0.33%151</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>63.6</v>
+        <v>151</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>0.20%306,000</t>
+          <t>0.23%629,000</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K301" t="n">
-        <v>306000</v>
+        <v>629000</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -18814,56 +18814,58 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>6981MURATA MANUFACTURING CO LTD</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>+6.01%</t>
-        </is>
-      </c>
-      <c r="H302" t="n">
-        <v>123.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>0.20%171,000</t>
+          <t>3.57%935,600</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K302" t="n">
-        <v>171000</v>
+        <v>935600</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -18875,56 +18877,58 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>1802台灣玻璃工業</t>
+          <t>009150SAMSUNG ELECTRO-MECHANICS CO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>-1.22%56.9</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>-1.22%</t>
-        </is>
-      </c>
-      <c r="H303" t="n">
-        <v>56.9</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>0.20%357,000</t>
+          <t>3.54%42,083</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K303" t="n">
-        <v>357000</v>
+        <v>42083</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -18936,56 +18940,58 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>-0.92%1075</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="H304" t="n">
-        <v>2050</v>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>0.20%9,000</t>
+          <t>3.43%1,146,000</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K304" t="n">
-        <v>9000</v>
+        <v>1146000</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -18997,56 +19003,58 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:18</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2049上銀科技</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-1.58%343.5</t>
+          <t>-4.4%5430</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>-1.58%</t>
-        </is>
-      </c>
-      <c r="H305" t="n">
-        <v>343.5</v>
+          <t>-4.4%</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>5430</t>
+        </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>0.19%55,000</t>
+          <t>3.33%212,000</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K305" t="n">
-        <v>55000</v>
+        <v>212000</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -19058,56 +19066,58 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:19</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>+2.09%2200</t>
+          <t>-1.45%2375</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>+2.09%</t>
-        </is>
-      </c>
-      <c r="H306" t="n">
-        <v>2200</v>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>0.17%8,000</t>
+          <t>2.53%406,000</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K306" t="n">
-        <v>8000</v>
+        <v>406000</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -19119,56 +19129,58 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:19</t>
+          <t>2026-08-24 16:25:34</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2317鴻海精密工業</t>
+          <t>000660SK HYNIX INC</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>-0.81%243.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>-0.81%</t>
-        </is>
-      </c>
-      <c r="H307" t="n">
-        <v>243.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>0.16%64,000</t>
+          <t>2.15%21,113</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K307" t="n">
-        <v>64000</v>
+        <v>21113</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -19180,56 +19192,58 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:19</t>
+          <t>2026-08-24 16:25:36</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>-0.86%1735</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>-1.43%</t>
-        </is>
-      </c>
-      <c r="H308" t="n">
-        <v>2070</v>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>0.10%5,000</t>
+          <t>2.02%441,000</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K308" t="n">
-        <v>5000</v>
+        <v>441000</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -19241,56 +19255,58 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:19</t>
+          <t>2026-08-24 16:25:36</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>6488環球晶圓</t>
+          <t>6857ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>+7.33%</t>
-        </is>
-      </c>
-      <c r="H309" t="n">
-        <v>1010</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>0.09%10,000</t>
+          <t>1.65%88,100</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K309" t="n">
-        <v>10000</v>
+        <v>88100</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -19302,59 +19318,502 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:19</t>
+          <t>2026-08-24 16:25:36</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>-2.1%</t>
-        </is>
-      </c>
-      <c r="H310" t="n">
-        <v>794</v>
+          <t>-2.68%</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>0.02%2,000</t>
+          <t>1.56%376,000</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K310" t="n">
-        <v>2000</v>
+        <v>376000</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>3</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2454聯發科</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-0.66%3765</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-0.66%</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>1.38%142,000</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="K311" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>3</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>6223旺矽</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>+1.83%5565</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>+1.83%</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>1.34%90,000</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>3</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>+0.85%592</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>0.99%641,000</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>641000</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>3</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>8046南電</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>0%1135</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>0.95%302,000</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>302000</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>3</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>+1.72%2070</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>0.95%172,000</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>172000</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>3</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>4062IBIDEN CO LTD</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>0.91%89,700</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="K316" t="n">
+        <v>89700</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:25:37</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>+3.02%239</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>+3.02%</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>0.62%1,008,000</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1008000</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-24_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-08-24_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:07</t>
+          <t>2026-08-24 16:55:37</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:08</t>
+          <t>2026-08-24 16:55:39</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:09</t>
+          <t>2026-08-24 16:55:40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:11</t>
+          <t>2026-08-24 16:55:41</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:11</t>
+          <t>2026-08-24 16:55:41</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:11</t>
+          <t>2026-08-24 16:55:41</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:11</t>
+          <t>2026-08-24 16:55:41</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:11</t>
+          <t>2026-08-24 16:55:41</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:17</t>
+          <t>2026-08-24 16:55:47</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:18</t>
+          <t>2026-08-24 16:55:49</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:19</t>
+          <t>2026-08-24 16:55:50</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:20</t>
+          <t>2026-08-24 16:55:51</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:20</t>
+          <t>2026-08-24 16:55:51</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:20</t>
+          <t>2026-08-24 16:55:51</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:20</t>
+          <t>2026-08-24 16:55:51</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:20</t>
+          <t>2026-08-24 16:55:51</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:47</t>
+          <t>2026-08-24 16:56:15</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:48</t>
+          <t>2026-08-24 16:56:16</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:49</t>
+          <t>2026-08-24 16:56:17</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:51</t>
+          <t>2026-08-24 16:56:19</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:51</t>
+          <t>2026-08-24 16:56:19</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:51</t>
+          <t>2026-08-24 16:56:19</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:51</t>
+          <t>2026-08-24 16:56:19</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:51</t>
+          <t>2026-08-24 16:56:19</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:03</t>
+          <t>2026-08-24 16:56:32</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:04</t>
+          <t>2026-08-24 16:56:33</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:04</t>
+          <t>2026-08-24 16:56:33</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:04</t>
+          <t>2026-08-24 16:56:33</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-08-24 16:43:06</t>
+          <t>2026-08-24 16:56:35</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
